--- a/GENESIS & TIDE.xlsx
+++ b/GENESIS & TIDE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohan\Desktop\Dashboard\GENESIS AND TIDE STARUPS IN MP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F370C884-7FD4-4A8F-9536-8F4AD6A1FCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E944EEB-685B-49F1-AEE8-0B307EECE696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GENESIS EIR 1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="112">
   <si>
     <t>S.no</t>
   </si>
@@ -355,12 +355,6 @@
     <t>S.No</t>
   </si>
   <si>
-    <t>AIC-ADT Baramati Foundation</t>
-  </si>
-  <si>
-    <t>Marathwada Accelerator for Growth and Incubation Council (MAGIC)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Name of Scheme </t>
   </si>
   <si>
@@ -374,6 +368,9 @@
   </si>
   <si>
     <t>ANUPAM Innovation and Incubation Center</t>
+  </si>
+  <si>
+    <t>ANUPAM INCUBATION AND INNOVATION CENTER, A UNIT OF KOTHIYA SOCIETY FOR SUSTAINABLE DEVELOPMENT AND RESEARCH</t>
   </si>
 </sst>
 </file>
@@ -460,13 +457,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -478,6 +468,13 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -666,19 +663,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1001,7 +998,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>7</v>
@@ -1015,7 +1012,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>8</v>
@@ -1167,7 +1164,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>21</v>
@@ -1181,7 +1178,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>22</v>
@@ -1195,7 +1192,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>23</v>
@@ -1209,7 +1206,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>24</v>
@@ -1428,7 +1425,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>48</v>
@@ -1525,7 +1522,7 @@
       <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -7556,36 +7553,36 @@
     <col min="2" max="2" width="22.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="26" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:2" s="25" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="25" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="B4" s="22" t="s">
         <v>107</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -7593,7 +7590,7 @@
         <v>81</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/GENESIS & TIDE.xlsx
+++ b/GENESIS & TIDE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rohan\Desktop\Dashboard\GENESIS AND TIDE STARUPS IN MP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEDBABA-4D90-4919-A530-36DC98A1CDBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D25B7A-71B9-4E97-A09C-0559212B772E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GENESIS EIR 1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="110">
   <si>
     <t>S.no</t>
   </si>
@@ -362,9 +362,6 @@
   </si>
   <si>
     <t>Incubator In Madhya Pradesh</t>
-  </si>
-  <si>
-    <t>ANUPAM Innovation and Incubation Center</t>
   </si>
   <si>
     <t>ANUPAM INCUBATION AND INNOVATION CENTER, A UNIT OF KOTHIYA SOCIETY FOR SUSTAINABLE DEVELOPMENT AND RESEARCH</t>
@@ -7501,7 +7498,7 @@
     </row>
     <row r="4" spans="1:2" s="1" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>106</v>
